--- a/Planilhas/Pedidos_logs2.xlsx
+++ b/Planilhas/Pedidos_logs2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4500032148</t>
+          <t>4500033536</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032148 modificado</t>
+          <t>Pedido Frete 4500033536 modificado</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4500032149</t>
+          <t>4500033802</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032149 modificado</t>
+          <t>Pedido Frete 4500033802 modificado</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4500032178</t>
+          <t>4500033803</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032178 modificado</t>
+          <t>Pedido Frete 4500033803 modificado</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4500032140</t>
+          <t>4500033804</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032140 modificado</t>
+          <t>Pedido Frete 4500033804 modificado</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4500032143</t>
+          <t>4500033805</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032143 modificado</t>
+          <t>Pedido Frete 4500033805 modificado</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4500032145</t>
+          <t>4500033812</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032145 modificado</t>
+          <t>Pedido Frete 4500033812 modificado</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4500032185</t>
+          <t>4500033813</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032185 modificado</t>
+          <t>Pedido Frete 4500033813 modificado</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4500032186</t>
+          <t>4500033814</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032186 modificado</t>
+          <t>Pedido Frete 4500033814 modificado</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4500032207</t>
+          <t>4500033815</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032207 modificado</t>
+          <t>Pedido Frete 4500033815 modificado</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4500032208</t>
+          <t>4500033816</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032208 modificado</t>
+          <t>Pedido Frete 4500033816 modificado</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4500032177</t>
+          <t>4500033817</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032177 modificado</t>
+          <t>Pedido Frete 4500033817 modificado</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4500032142</t>
+          <t>4500033818</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032142 modificado</t>
+          <t>Pedido Frete 4500033818 modificado</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4500032201</t>
+          <t>4500033819</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032201 modificado</t>
+          <t>Pedido Frete 4500033819 modificado</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4500032168</t>
+          <t>4500033820</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032168 modificado</t>
+          <t>Pedido Frete 4500033820 modificado</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4500032169</t>
+          <t>4500033821</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032169 modificado</t>
+          <t>Pedido Frete 4500033821 modificado</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4500032147</t>
+          <t>4500033827</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032147 modificado</t>
+          <t>Pedido Frete 4500033827 modificado</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4500032204</t>
+          <t>4500033829</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032204 modificado</t>
+          <t>Pedido Frete 4500033829 modificado</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4500032210</t>
+          <t>4500033831</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032210 modificado</t>
+          <t>Pedido Frete 4500033831 modificado</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4500032184</t>
+          <t>4500033832</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032184 modificado</t>
+          <t>Pedido Frete 4500033832 modificado</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4500032203</t>
+          <t>4500033833</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032203 modificado</t>
+          <t>Pedido Frete 4500033833 modificado</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4500032211</t>
+          <t>4500033835</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032211 modificado</t>
+          <t>Pedido Frete 4500033835 modificado</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4500032167</t>
+          <t>4500033836</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032167 modificado</t>
+          <t>Pedido Frete 4500033836 modificado</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4500032205</t>
+          <t>4500033837</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032205 modificado</t>
+          <t>Pedido Frete 4500033837 modificado</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4500032209</t>
+          <t>4500033841</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032209 modificado</t>
+          <t>Pedido Frete 4500033841 modificado</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4500032170</t>
+          <t>4500033851</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032170 modificado</t>
+          <t>Pedido Frete 4500033851 modificado</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4500032183</t>
+          <t>4500033852</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032183 modificado</t>
+          <t>Pedido Frete 4500033852 modificado</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4500032202</t>
+          <t>4500033853</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032202 modificado</t>
+          <t>Pedido Frete 4500033853 modificado</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4500032206</t>
+          <t>4500033854</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032206 modificado</t>
+          <t>Pedido Frete 4500033854 modificado</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4500032152</t>
+          <t>4500033855</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032152 modificado</t>
+          <t>Pedido Frete 4500033855 modificado</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4500032153</t>
+          <t>4500033856</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032153 modificado</t>
+          <t>Pedido Frete 4500033856 modificado</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4500032154</t>
+          <t>4500033857</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032154 modificado</t>
+          <t>Pedido Frete 4500033857 modificado</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4500032155</t>
+          <t>4500033858</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032155 modificado</t>
+          <t>Pedido Frete 4500033858 modificado</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4500032156</t>
+          <t>4500033859</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032156 modificado</t>
+          <t>Pedido Frete 4500033859 modificado</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4500032157</t>
+          <t>4500033860</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032157 modificado</t>
+          <t>Pedido Frete 4500033860 modificado</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>4500032158</t>
+          <t>4500033861</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032158 modificado</t>
+          <t>Pedido Frete 4500033861 modificado</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4500032159</t>
+          <t>4500033862</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032159 modificado</t>
+          <t>Pedido Frete 4500033862 modificado</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4500032160</t>
+          <t>4500033863</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032160 modificado</t>
+          <t>Pedido Frete 4500033863 modificado</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>4500032161</t>
+          <t>4500033864</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032161 modificado</t>
+          <t>Pedido Frete 4500033864 modificado</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4500032162</t>
+          <t>4500033872</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032162 modificado</t>
+          <t>Pedido Frete 4500033872 modificado</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4500032163</t>
+          <t>4500033874</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032163 modificado</t>
+          <t>Pedido Frete 4500033874 modificado</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4500032165</t>
+          <t>4500033875</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032165 modificado</t>
+          <t>Pedido Frete 4500033875 modificado</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4500032166</t>
+          <t>4500033876</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032166 modificado</t>
+          <t>Pedido Frete 4500033876 modificado</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4500032171</t>
+          <t>4500033877</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032171 modificado</t>
+          <t>Pedido Frete 4500033877 modificado</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4500032172</t>
+          <t>4500033878</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032172 modificado</t>
+          <t>Pedido Frete 4500033878 modificado</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4500032173</t>
+          <t>4500033801</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032173 modificado</t>
+          <t>Pedido Frete 4500033801 modificado</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>4500032174</t>
+          <t>4500033822</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032174 modificado</t>
+          <t>Pedido Frete 4500033822 modificado</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4500032175</t>
+          <t>4500033823</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032175 modificado</t>
+          <t>Pedido Frete 4500033823 modificado</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4500032176</t>
+          <t>4500033824</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032176 modificado</t>
+          <t>Pedido Frete 4500033824 modificado</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4500032180</t>
+          <t>4500033825</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032180 modificado</t>
+          <t>Pedido Frete 4500033825 modificado</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4500032181</t>
+          <t>4500033826</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032181 modificado</t>
+          <t>Pedido Frete 4500033826 modificado</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4500032182</t>
+          <t>4500033838</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032182 modificado</t>
+          <t>Pedido Frete 4500033838 modificado</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4500032187</t>
+          <t>4500033839</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032187 modificado</t>
+          <t>Pedido Frete 4500033839 modificado</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4500032188</t>
+          <t>4500033840</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032188 modificado</t>
+          <t>Pedido Frete 4500033840 modificado</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4500032189</t>
+          <t>4500033842</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032189 modificado</t>
+          <t>Pedido Frete 4500033842 modificado</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4500032190</t>
+          <t>4500033843</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032190 modificado</t>
+          <t>Pedido Frete 4500033843 modificado</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4500032191</t>
+          <t>4500033844</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032191 modificado</t>
+          <t>Pedido Frete 4500033844 modificado</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>4500032192</t>
+          <t>4500033846</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032192 modificado</t>
+          <t>Pedido Frete 4500033846 modificado</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>4500032193</t>
+          <t>4500033847</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032193 modificado</t>
+          <t>Pedido Frete 4500033847 modificado</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4500032194</t>
+          <t>4500033848</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032194 modificado</t>
+          <t>Pedido Frete 4500033848 modificado</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4500032195</t>
+          <t>4500033849</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032195 modificado</t>
+          <t>Pedido Frete 4500033849 modificado</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4500032196</t>
+          <t>4500033850</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032196 modificado</t>
+          <t>Pedido Frete 4500033850 modificado</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4500032197</t>
+          <t>4500033865</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032197 modificado</t>
+          <t>Pedido Frete 4500033865 modificado</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4500032198</t>
+          <t>4500033866</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032198 modificado</t>
+          <t>Pedido Frete 4500033866 modificado</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4500032199</t>
+          <t>4500033867</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032199 modificado</t>
+          <t>Pedido Frete 4500033867 modificado</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4500032200</t>
+          <t>4500033868</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032200 modificado</t>
+          <t>Pedido Frete 4500033868 modificado</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4500032212</t>
+          <t>4500033869</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032212 modificado</t>
+          <t>Pedido Frete 4500033869 modificado</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4500032213</t>
+          <t>4500033870</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3134,207 +3134,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pedido Frete 4500032213 modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>69</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>4500032214</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>RAZAO</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>3201010111</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Pedido Frete 4500032214 modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>70</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>4500032215</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>RAZAO</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>3201010111</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Pedido Frete 4500032215 modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>71</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>4500032216</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>RAZAO</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>3201010111</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Pedido Frete 4500032216 modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>72</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>4500032217</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>RAZAO</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>3201010111</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Pedido Frete 4500032217 modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>73</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>4500032218</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>00010</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>RAZAO</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>3201010111</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>F5</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>SUCESSO</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Pedido Frete 4500032218 modificado</t>
+          <t>Pedido Frete 4500033870 modificado</t>
         </is>
       </c>
     </row>
